--- a/Figure 2/Figure 2-N.xlsx
+++ b/Figure 2/Figure 2-N.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\iMetaOmics20260210\Figure 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94E53268-394A-4937-9143-12619E8F0721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83ED3BBC-C6AE-4823-A0E5-7EEC62AC5035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30630" yWindow="1690" windowWidth="15760" windowHeight="15580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28790" yWindow="4080" windowWidth="16730" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -83,7 +83,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -103,6 +103,12 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -125,12 +131,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -419,135 +429,136 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="4">
         <v>0.33427988433320172</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="4">
         <v>0.64107173382468252</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="4">
         <v>0.77883866242014144</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="4">
         <v>0.47645559901668549</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="4">
         <v>0.26708890105805089</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="4">
         <v>0.39749380756349428</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="4">
         <v>0.51971288026793194</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="4">
         <v>0.29445515280491208</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="4">
         <v>0.28437998773689555</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="4">
         <v>0.31854090262945017</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="4">
         <v>0.41977903327163285</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="4">
         <v>0.31644647992823521</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="4">
         <v>0.46114434676550037</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="4">
         <v>0.48951906079109131</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="4">
         <v>0.57910050884106845</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="4">
         <v>0.39555446676334821</v>
       </c>
     </row>
